--- a/Result/profitability/1781.xlsx
+++ b/Result/profitability/1781.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.19875</v>
+        <v>-0.275</v>
       </c>
       <c r="N2" t="n">
-        <v>18.49125</v>
+        <v>17.505</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2875</v>
+        <v>-0.34625</v>
       </c>
       <c r="N3" t="n">
-        <v>16.7775</v>
+        <v>15.4925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.29625</v>
+        <v>-0.35125</v>
       </c>
       <c r="N4" t="n">
-        <v>14.9825</v>
+        <v>13.58375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.68</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.39625</v>
+        <v>-0.32875</v>
       </c>
       <c r="N5" t="n">
-        <v>12.17875</v>
+        <v>12.47625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.31875</v>
+        <v>-0.31125</v>
       </c>
       <c r="N6" t="n">
-        <v>11.45125</v>
+        <v>11.5575</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-1.12</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.41125</v>
+        <v>-0.42875</v>
       </c>
       <c r="N7" t="n">
-        <v>11.3725</v>
+        <v>11.96375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3875</v>
+        <v>-0.4037500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>11.6575</v>
+        <v>12.115</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>96</v>
+      </c>
+      <c r="D75" t="n">
+        <v>81</v>
+      </c>
+      <c r="E75" t="n">
+        <v>16</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-16.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.17125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.3975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6842105263157894</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2923322683706071</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6279069767441861</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.379999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.172463768115942</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
